--- a/Sample_run/1/student/cuongnvhe181200/TC1/GradeDetail.xlsx
+++ b/Sample_run/1/student/cuongnvhe181200/TC1/GradeDetail.xlsx
@@ -158,9 +158,6 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
-    <x:t>SYN_SENT</x:t>
-  </x:si>
-  <x:si>
     <x:t>PASS</x:t>
   </x:si>
   <x:si>
@@ -182,10 +179,10 @@
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
-    <x:t>RST-ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RESET</x:t>
+    <x:t>RST, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Connection reset</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -929,7 +926,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="29.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1029,7 +1026,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
         <x:v>44</x:v>
@@ -1041,13 +1038,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>35828</x:v>
+        <x:v>39878</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:18">
@@ -1067,10 +1064,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
@@ -1082,28 +1079,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R3" s="3" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R3" s="3" t="s">
-        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18">
@@ -1111,7 +1108,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>17</x:v>
@@ -1141,7 +1138,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
         <x:v>44</x:v>
@@ -1153,13 +1150,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>35790</x:v>
+        <x:v>59252</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
       </x:c>
       <x:c r="R4" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:18">
@@ -1167,7 +1164,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>17</x:v>
@@ -1194,10 +1191,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="L5" s="0" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
         <x:v>45</x:v>
@@ -1212,10 +1209,10 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>35790</x:v>
+        <x:v>59252</x:v>
       </x:c>
       <x:c r="R5" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:18">
@@ -1223,7 +1220,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>17</x:v>
@@ -1250,10 +1247,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="L6" s="0" t="s">
-        <x:v>55</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
         <x:v>45</x:v>
@@ -1268,10 +1265,10 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>35828</x:v>
+        <x:v>39878</x:v>
       </x:c>
       <x:c r="R6" s="4" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Sample_run/1/student/cuongnvhe181200/TC1/GradeDetail.xlsx
+++ b/Sample_run/1/student/cuongnvhe181200/TC1/GradeDetail.xlsx
@@ -1038,7 +1038,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>39878</x:v>
+        <x:v>36260</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1150,7 +1150,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>59252</x:v>
+        <x:v>42908</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1209,7 +1209,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q5" s="0">
-        <x:v>59252</x:v>
+        <x:v>42908</x:v>
       </x:c>
       <x:c r="R5" s="4" t="s">
         <x:v>52</x:v>
@@ -1265,7 +1265,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>39878</x:v>
+        <x:v>36260</x:v>
       </x:c>
       <x:c r="R6" s="4" t="s">
         <x:v>52</x:v>
